--- a/day7.xlsx
+++ b/day7.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/utkarsh/Downloads/Accio_excel/Excel-for-DA/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0380B12E-E9AB-4748-8A8D-CE2089590C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E63D3C3-AF61-4B4F-B8FA-9628291C5906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="600" windowWidth="28800" windowHeight="17400" activeTab="3" xr2:uid="{2DB0D99C-D0EA-554B-AB8A-01A4483518E8}"/>
   </bookViews>
@@ -20,15 +20,23 @@
   </sheets>
   <definedNames>
     <definedName name="solver_eng" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_eng" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_lin" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_lin" localSheetId="3" hidden="1">2</definedName>
     <definedName name="solver_neg" localSheetId="2" hidden="1">1</definedName>
+    <definedName name="solver_neg" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_num" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_num" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_opt" localSheetId="2" hidden="1">Sheet3!$G$11</definedName>
+    <definedName name="solver_opt" localSheetId="3" hidden="1">Sheet4!$N$52</definedName>
     <definedName name="solver_typ" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_typ" localSheetId="3" hidden="1">1</definedName>
     <definedName name="solver_val" localSheetId="2" hidden="1">0</definedName>
+    <definedName name="solver_val" localSheetId="3" hidden="1">0</definedName>
     <definedName name="solver_ver" localSheetId="2" hidden="1">2</definedName>
+    <definedName name="solver_ver" localSheetId="3" hidden="1">2</definedName>
   </definedNames>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -71,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="194" uniqueCount="152">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="152">
   <si>
     <t>Logical Functions</t>
   </si>
@@ -481,12 +489,6 @@
     <t>Upper 95%</t>
   </si>
   <si>
-    <t>Lower 95.0%</t>
-  </si>
-  <si>
-    <t>Upper 95.0%</t>
-  </si>
-  <si>
     <t>1) Is there a reln b/w X and Y</t>
   </si>
   <si>
@@ -496,9 +498,6 @@
     <t>3) How good is the Input Variable for prediction of Y</t>
   </si>
   <si>
-    <t>Salary = intercept + slope * ( YOE)</t>
-  </si>
-  <si>
     <t>Y = c + m*x</t>
   </si>
   <si>
@@ -527,6 +526,15 @@
   </si>
   <si>
     <t>95.69% of Variance in Y can be Explained ( captured) using YOE</t>
+  </si>
+  <si>
+    <t>Lower 99.0%</t>
+  </si>
+  <si>
+    <t>Upper 99.0%</t>
+  </si>
+  <si>
+    <t>is there a reln ( Linear Reln) for Statistical purpose</t>
   </si>
 </sst>
 </file>
@@ -673,21 +681,14 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="31">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
@@ -695,10 +696,19 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -707,16 +717,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="centerContinuous"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1843,8 +1843,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>53257</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="2" name="Ink 1">
@@ -1863,7 +1863,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="2" name="Ink 1">
@@ -1908,8 +1908,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>82057</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="3" name="Ink 2">
@@ -1928,7 +1928,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="3" name="Ink 2">
@@ -1973,8 +1973,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>98916</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="6" name="Ink 5">
@@ -1993,7 +1993,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="6" name="Ink 5">
@@ -2038,8 +2038,8 @@
       <xdr:row>24</xdr:row>
       <xdr:rowOff>114817</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId7">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="7" name="Ink 6">
@@ -2058,7 +2058,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="7" name="Ink 6">
@@ -2103,8 +2103,8 @@
       <xdr:row>25</xdr:row>
       <xdr:rowOff>131676</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId9">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="10" name="Ink 9">
@@ -2123,7 +2123,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="10" name="Ink 9">
@@ -2168,8 +2168,8 @@
       <xdr:row>29</xdr:row>
       <xdr:rowOff>37112</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="16" name="Ink 15">
@@ -2188,7 +2188,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="16" name="Ink 15">
@@ -2233,8 +2233,8 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>20946</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="19" name="Ink 18">
@@ -2253,7 +2253,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="19" name="Ink 18">
@@ -2298,8 +2298,8 @@
       <xdr:row>44</xdr:row>
       <xdr:rowOff>178986</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId15">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="26" name="Ink 25">
@@ -2318,7 +2318,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="26" name="Ink 25">
@@ -2363,8 +2363,8 @@
       <xdr:row>67</xdr:row>
       <xdr:rowOff>190098</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId17">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="30" name="Ink 29">
@@ -2383,7 +2383,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="30" name="Ink 29">
@@ -2428,8 +2428,8 @@
       <xdr:row>139</xdr:row>
       <xdr:rowOff>138443</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId19">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="48" name="Ink 47">
@@ -2448,7 +2448,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="48" name="Ink 47">
@@ -2525,136 +2525,6 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>86960</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>120320</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>188120</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>197000</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="4" name="Ink 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E85C98-07E9-A2BA-A63A-83F3CF8CA3A4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="7788240" y="933120"/>
-            <a:ext cx="101160" cy="1905480"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="4" name="Ink 3">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{28E85C98-07E9-A2BA-A63A-83F3CF8CA3A4}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId3"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="7782120" y="927000"/>
-              <a:ext cx="113400" cy="1917720"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>470360</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>180240</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>713977</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>49560</xdr:rowOff>
-    </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4">
-          <xdr14:nvContentPartPr>
-            <xdr14:cNvPr id="9" name="Ink 8">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD936CF-758C-E91F-E415-B3E31C219594}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr14:cNvPr>
-            <xdr14:cNvContentPartPr/>
-          </xdr14:nvContentPartPr>
-          <xdr14:nvPr macro=""/>
-          <xdr14:xfrm>
-            <a:off x="4056840" y="789840"/>
-            <a:ext cx="4214880" cy="1698120"/>
-          </xdr14:xfrm>
-        </xdr:contentPart>
-      </mc:Choice>
-      <mc:Fallback>
-        <xdr:pic>
-          <xdr:nvPicPr>
-            <xdr:cNvPr id="9" name="Ink 8">
-              <a:extLst>
-                <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-                  <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACD936CF-758C-E91F-E415-B3E31C219594}"/>
-                </a:ext>
-              </a:extLst>
-            </xdr:cNvPr>
-            <xdr:cNvPicPr/>
-          </xdr:nvPicPr>
-          <xdr:blipFill>
-            <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId5"/>
-            <a:stretch>
-              <a:fillRect/>
-            </a:stretch>
-          </xdr:blipFill>
-          <xdr:spPr>
-            <a:xfrm>
-              <a:off x="4050719" y="783720"/>
-              <a:ext cx="4227121" cy="1710360"/>
-            </a:xfrm>
-            <a:prstGeom prst="rect">
-              <a:avLst/>
-            </a:prstGeom>
-          </xdr:spPr>
-        </xdr:pic>
-      </mc:Fallback>
-    </mc:AlternateContent>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>5</xdr:col>
       <xdr:colOff>664060</xdr:colOff>
       <xdr:row>35</xdr:row>
@@ -2663,12 +2533,12 @@
     <xdr:to>
       <xdr:col>8</xdr:col>
       <xdr:colOff>909680</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>6960</xdr:rowOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>193227</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
-        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
+        <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="12" name="Ink 11">
               <a:extLst>
@@ -2686,7 +2556,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="12" name="Ink 11">
@@ -2731,8 +2601,8 @@
       <xdr:row>47</xdr:row>
       <xdr:rowOff>68920</xdr:rowOff>
     </xdr:to>
-    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-      <mc:Choice xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" Requires="xdr14">
+    <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing">
+      <mc:Choice Requires="xdr14">
         <xdr:contentPart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId8">
           <xdr14:nvContentPartPr>
             <xdr14:cNvPr id="13" name="Ink 12">
@@ -2751,7 +2621,7 @@
           </xdr14:xfrm>
         </xdr:contentPart>
       </mc:Choice>
-      <mc:Fallback>
+      <mc:Fallback xmlns="">
         <xdr:pic>
           <xdr:nvPicPr>
             <xdr:cNvPr id="13" name="Ink 12">
@@ -2871,64 +2741,6 @@
           <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
         </inkml:channelProperties>
       </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-04-07T17:27:59.641"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">281 5293 24575,'0'-30'0,"0"-29"0,0-33 0,0 30 0,0-3 0,0-5 0,0 0 0,0 2 0,0 1 0,0 5 0,0 1 0,0 7 0,0 2 0,0-46 0,0 48 0,0-1 0,0 0 0,0-1 0,0-2 0,0-1 0,0-2 0,0-2 0,0-4 0,0-3 0,0-9 0,0-2 0,0-3 0,0-1 0,0-1 0,0 1 0,0 4 0,0 2 0,0 9 0,0 2 0,0 5 0,0 1 0,0 5 0,0 1 0,0-42 0,0 2 0,0 1 0,0 0 0,-1-3 0,-3 4 0,-3-1 0,-3 1 0,-3 0 0,0 0 0,0 2 0,-1 4 0,1 0 0,0-6 0,6 41 0,-1-2 0,1-2 0,-2-1 0,0-2 0,-1 1 0,0 0 0,1 2 0,-9-43 0,2 10 0,4 17 0,3 17 0,5 14 0,3 13 0,1 8 0,0 5 0,0 1 0,0 0 0,0-5 0,0-7 0,0-13 0,0-20 0,0-15 0,0-9 0,-3 0 0,0 11 0,-1 13 0,-1 16 0,3 14 0,1 11 0,1 5 0,0 0 0,0-1 0,0-4 0,-2-6 0,-2-6 0,-3-2 0,1 2 0,0 10 0,2 10 0,2 13 0,1 12 0,0 8 0,1 19 0,0-24 0,0 6 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
-      <inkml:timestamp xml:id="ts0" timeString="2026-04-07T17:28:02.757"/>
-    </inkml:context>
-    <inkml:brush xml:id="br0">
-      <inkml:brushProperty name="width" value="0.035" units="cm"/>
-      <inkml:brushProperty name="height" value="0.035" units="cm"/>
-      <inkml:brushProperty name="color" value="#E71224"/>
-    </inkml:brush>
-  </inkml:definitions>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0">1 623 24575,'8'-3'0,"23"1"0,45 0 0,-12 2 0,10 0 0,-8 0 0,5 0 0,4 0-750,16 0 0,4 0 0,2 0 750,-16 0 0,2 0 0,1 0 0,1 0 0,6 0 0,1 0 0,1 0 0,0 0-356,1 0 1,2 0-1,-1 0 1,0 0 355,-1 0 0,1 0 0,-1 0 0,0 0 0,-1 0 0,-1 0 0,1 0 0,-1 0 0,-3 0 0,1 0 0,-1 0 0,-2 0-263,-5 0 1,0 0 0,-2 0 0,-2 0 262,19 0 0,-2 0 0,-3 0-98,-9 0 0,-3 0 0,-3 0 98,21 0 0,-5 0 705,-10 0 1,-4 0-706,-11 0 0,-2 0 984,-5 0 0,0 0-984,1 0 0,1 0 627,2 0 0,0 0-627,3 0 0,2 0 191,4 0 0,2 0-191,4 0 0,1 0 0,6 0 0,1 0 0,5 0 0,0-1 0,1-1 0,0-1 0,2-1 0,1 1 0,2-1 0,1-1-166,-31 1 0,0 0 0,0 1 166,2 0 0,0 0 0,-1 0 0,2 0 0,0-1 0,0 0 0,-2 1 0,-1 0 0,0 0 0,0 0 0,-1 1 0,-1 0 0,30-2 0,-1 0 0,-7 2 0,-2 0 0,-7 0 0,-3 0 0,-9 1 0,-1 0 0,-2 1 0,1 0 0,-5 0 0,1 0 0,2 0 0,0 0 249,4 0 0,1 0-249,-1 0 0,2-1 0,3 0 0,0-1 0,1-1 0,-1 0 0,1 0 0,-1 0 0,0-1 0,1 0 0,-2 1 0,0 1 0,-2 0 0,-2-1 0,-3 0 0,-2-1 0,-5 1 0,-2 1 0,-4-2 0,-2 0 0,38-4 0,-10 2 0,-8-1 0,-8 1 0,-6 0 0,-12 2 0,-10 2 0,-8 2 0,-7 0 0,-3 0 0,-7 0 0,-6 0 0,-7-4-1696,-7-4 0,6 2 0,-1-1 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="1700">10207 339 24575,'-8'-6'0,"6"2"0,3 1 0,13 0 0,7-5 0,3-8 0,-3-7 0,-10-8 0,-11 4 0,-14 4 0,-12 8 0,-7 10 0,-2 15 0,5 22 0,11 22 0,9 17 0,6 0 0,5-11 0,5-16 0,7-18 0,6-12 0,4-9 0,3-9 0,2-14 0,-4-15 0,-6-14 0,-9-1 0,-11 11 0,-11 14 0,-9 13 0,-5 7 0,3 7 0,7 10 0,8 9 0,5 8 0,3 1 0,2-7 0,4-7 0,4-7 0,5-5 0,6-4 0,1-6 0,1-6 0,-4-4 0,-7-3 0,-8 4 0,-10 3 0,-8 5 0,-6 4 0,0 4 0,5 6 0,6 4 0,6 3 0,2-1 0,2-7 0,0-3 0</inkml:trace>
-  <inkml:trace contextRef="#ctx0" brushRef="#br0" timeOffset="4417">405 4716 24575,'27'-3'0,"30"-5"0,-7 1 0,5-4 0,17-6 0,5-5 0,11-6 0,3-4 0,-27 9 0,0-2 0,1-1 0,-2 0 0,-1-1 0,1 0 0,-1 1 0,0 0 0,-1 0 0,1 0 0,0-1 0,0 0 0,1 0 0,1-1 0,0 0 0,-1 1 0,1 1 0,-1-2 0,-2 1 0,0 0 0,0 0 0,25-12 0,-2 2 0,-8 5 0,-1 0 0,0 2 0,-2 1 0,-4 3 0,-2 1 0,-3 3 0,-1 0 0,-3 2 0,-2 0 0,-8 3 0,-2 0 0,38-14 0,-17 3 0,-11 0 0,-3 1 0,5-3 0,19-9 0,-23 14 0,6-3 0,23-12 0,8-4-464,-16 6 1,5-2 0,2-1 463,-17 7 0,2 0 0,0 0 0,-1-1 0,1 0 0,-1 0 0,0 0 0,-1 2 0,13-7 0,-1 1 0,-3 3-46,-11 5 0,-3 3 0,0 1 46,24-9 0,-2 3 0,-5 2 0,1 2 0,4-2 0,2 1 0,-24 8 0,2-1 0,1 0 0,2-2 0,2 0 0,0-1-266,5-1 1,2 0 0,-1-1 265,4-2 0,-1-1 0,1 0 0,2-2 0,1 0 0,-1-2 0,2 0 0,0-2 0,0 0 0,-2-1 0,-1 0 0,0 0 0,-4 1 0,-1 0 0,-2 0 0,-5 4 0,-2 0 0,-2 1 0,23-10 0,-3 2 0,-11 5 0,-3 2 661,-8 4 0,-3 1-661,-5 3 0,-3 1 71,-5 2 0,-1 0-71,35-16 860,-9 4-860,-4 5 0,-6 3 0,0 3 0,3-3 0,3-3 0,7-4 0,1-7 0,2 0 0,-2-3 0,-3 3 0,0 1 0,-2 2 0,0 0 0,-3 3 0,-5 3 0,-8 1 0,-7 1 0,-3 1 0,0-2 0,0 0 0,0-3 0,-3-3 0,0 0 0,1-2 0,4 0 0,6 0 0,5 1 0,8 0 0,7-1 0,7 0 0,7 0 0,4-1 0,-44 20 0,1 0 0,45-17 0,-43 20 0,2 1 0,4 0 0,2 3 0,5-1 0,1 1 0,3 1 0,0 1 0,-3 2 0,-1 0 0,-5 2 0,-1 2 0,40-1 0,-15 2 0,-14 3 0,-14 0 0,-10 0 0,-12-1 0,-9-2 0,-4-2 0,-4-1 0,-6 2 0,-3 1 0</inkml:trace>
-</inkml:ink>
-</file>
-
-<file path=xl/ink/ink13.xml><?xml version="1.0" encoding="utf-8"?>
-<inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
-  <inkml:definitions>
-    <inkml:context xml:id="ctx0">
-      <inkml:inkSource xml:id="inkSrc0">
-        <inkml:traceFormat>
-          <inkml:channel name="X" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="Y" type="integer" min="-2.14748E9" max="2.14748E9" units="cm"/>
-          <inkml:channel name="F" type="integer" max="32767" units="dev"/>
-        </inkml:traceFormat>
-        <inkml:channelProperties>
-          <inkml:channelProperty channel="X" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="Y" name="resolution" value="1000" units="1/cm"/>
-          <inkml:channelProperty channel="F" name="resolution" value="0" units="1/dev"/>
-        </inkml:channelProperties>
-      </inkml:inkSource>
       <inkml:timestamp xml:id="ts0" timeString="2026-04-07T17:35:50.403"/>
     </inkml:context>
     <inkml:brush xml:id="br0">
@@ -2942,7 +2754,7 @@
 </inkml:ink>
 </file>
 
-<file path=xl/ink/ink14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/ink/ink12.xml><?xml version="1.0" encoding="utf-8"?>
 <inkml:ink xmlns:inkml="http://www.w3.org/2003/InkML">
   <inkml:definitions>
     <inkml:context xml:id="ctx0">
@@ -3529,16 +3341,16 @@
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="2" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B2" s="2" t="s">
+      <c r="B2" s="19" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2"/>
-      <c r="D2" s="2"/>
+      <c r="C2" s="19"/>
+      <c r="D2" s="19"/>
     </row>
     <row r="3" spans="2:4" x14ac:dyDescent="0.2">
-      <c r="B3" s="2"/>
-      <c r="C3" s="2"/>
-      <c r="D3" s="2"/>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
     </row>
     <row r="5" spans="2:4" x14ac:dyDescent="0.2">
       <c r="B5" t="s">
@@ -3661,12 +3473,12 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.2">
-      <c r="A45" s="3"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
+      <c r="A45" s="1"/>
+      <c r="B45" s="1"/>
+      <c r="C45" s="1"/>
+      <c r="D45" s="1"/>
+      <c r="E45" s="1"/>
+      <c r="F45" s="1"/>
     </row>
     <row r="49" spans="2:2" x14ac:dyDescent="0.2">
       <c r="B49" t="s">
@@ -3712,16 +3524,16 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A11" s="3"/>
-      <c r="B11" s="3"/>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3"/>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3"/>
-      <c r="G11" s="3"/>
+      <c r="A11" s="1"/>
+      <c r="B11" s="1"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B13" s="3" t="b">
+      <c r="B13" s="1" t="b">
         <v>1</v>
       </c>
       <c r="C13">
@@ -3729,7 +3541,7 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B14" s="3" t="b">
+      <c r="B14" s="1" t="b">
         <v>0</v>
       </c>
       <c r="C14">
@@ -3737,13 +3549,13 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A17" s="3"/>
-      <c r="B17" s="3"/>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3"/>
-      <c r="E17" s="3"/>
-      <c r="F17" s="3"/>
-      <c r="G17" s="3"/>
+      <c r="A17" s="1"/>
+      <c r="B17" s="1"/>
+      <c r="C17" s="1"/>
+      <c r="D17" s="1"/>
+      <c r="E17" s="1"/>
+      <c r="F17" s="1"/>
+      <c r="G17" s="1"/>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B20" t="s">
@@ -3865,12 +3677,12 @@
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="3"/>
-      <c r="B35" s="3"/>
-      <c r="C35" s="3"/>
-      <c r="D35" s="3"/>
-      <c r="E35" s="3"/>
-      <c r="F35" s="3"/>
+      <c r="A35" s="1"/>
+      <c r="B35" s="1"/>
+      <c r="C35" s="1"/>
+      <c r="D35" s="1"/>
+      <c r="E35" s="1"/>
+      <c r="F35" s="1"/>
     </row>
     <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B37" t="s">
@@ -3916,25 +3728,25 @@
       </c>
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A48" s="3"/>
-      <c r="B48" s="3"/>
-      <c r="C48" s="3"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="3"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="3"/>
-      <c r="H48" s="3"/>
-      <c r="I48" s="3"/>
+      <c r="A48" s="1"/>
+      <c r="B48" s="1"/>
+      <c r="C48" s="1"/>
+      <c r="D48" s="1"/>
+      <c r="E48" s="1"/>
+      <c r="F48" s="1"/>
+      <c r="G48" s="1"/>
+      <c r="H48" s="1"/>
+      <c r="I48" s="1"/>
     </row>
     <row r="50" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B50" s="1" t="s">
+      <c r="B50" s="20" t="s">
         <v>20</v>
       </c>
-      <c r="C50" s="1"/>
+      <c r="C50" s="20"/>
     </row>
     <row r="51" spans="2:5" x14ac:dyDescent="0.2">
-      <c r="B51" s="1"/>
-      <c r="C51" s="1"/>
+      <c r="B51" s="20"/>
+      <c r="C51" s="20"/>
     </row>
     <row r="53" spans="2:5" x14ac:dyDescent="0.2">
       <c r="C53" t="s">
@@ -3973,27 +3785,27 @@
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B70" s="4" t="s">
+      <c r="B70" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C70" s="4" t="s">
+      <c r="C70" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D70" s="4" t="s">
+      <c r="D70" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F70" s="6" t="s">
+      <c r="F70" s="4" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B71" s="5" t="s">
+      <c r="B71" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C71" s="5">
+      <c r="C71" s="3">
         <v>4000</v>
       </c>
-      <c r="D71" s="5">
+      <c r="D71" s="3">
         <v>17</v>
       </c>
       <c r="F71" t="b">
@@ -4006,13 +3818,13 @@
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C72" s="5">
+      <c r="C72" s="3">
         <v>5600</v>
       </c>
-      <c r="D72" s="5">
+      <c r="D72" s="3">
         <v>18</v>
       </c>
       <c r="F72" t="b">
@@ -4025,13 +3837,13 @@
       </c>
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B73" s="5" t="s">
+      <c r="B73" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C73" s="5">
+      <c r="C73" s="3">
         <v>9700</v>
       </c>
-      <c r="D73" s="5">
+      <c r="D73" s="3">
         <v>19</v>
       </c>
       <c r="F73" t="b">
@@ -4044,13 +3856,13 @@
       </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B74" s="5" t="s">
+      <c r="B74" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C74" s="5">
+      <c r="C74" s="3">
         <v>4000</v>
       </c>
-      <c r="D74" s="5">
+      <c r="D74" s="3">
         <v>20</v>
       </c>
       <c r="F74" t="b">
@@ -4063,35 +3875,35 @@
       </c>
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A75" s="7"/>
-      <c r="B75" s="8" t="s">
+      <c r="A75" s="5"/>
+      <c r="B75" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C75" s="8">
+      <c r="C75" s="6">
         <v>8000</v>
       </c>
-      <c r="D75" s="8">
+      <c r="D75" s="6">
         <v>21</v>
       </c>
-      <c r="E75" s="7"/>
-      <c r="F75" s="7" t="b">
+      <c r="E75" s="5"/>
+      <c r="F75" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G75" s="7"/>
+      <c r="G75" s="5"/>
       <c r="I75" t="str">
         <f t="shared" si="2"/>
         <v>ADULT FROM MAHARASTRA</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B76" s="5" t="s">
+      <c r="B76" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C76" s="5">
+      <c r="C76" s="3">
         <v>9000</v>
       </c>
-      <c r="D76" s="5">
+      <c r="D76" s="3">
         <v>17</v>
       </c>
       <c r="F76" t="b">
@@ -4104,13 +3916,13 @@
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B77" s="5" t="s">
+      <c r="B77" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C77" s="5">
+      <c r="C77" s="3">
         <v>15000</v>
       </c>
-      <c r="D77" s="5">
+      <c r="D77" s="3">
         <v>18</v>
       </c>
       <c r="F77" t="b">
@@ -4123,13 +3935,13 @@
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B78" s="5" t="s">
+      <c r="B78" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C78" s="5">
+      <c r="C78" s="3">
         <v>34000</v>
       </c>
-      <c r="D78" s="5">
+      <c r="D78" s="3">
         <v>16</v>
       </c>
       <c r="F78" t="b">
@@ -4142,13 +3954,13 @@
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="B79" s="5" t="s">
+      <c r="B79" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C79" s="5">
+      <c r="C79" s="3">
         <v>9000</v>
       </c>
-      <c r="D79" s="5">
+      <c r="D79" s="3">
         <v>20</v>
       </c>
       <c r="F79" t="b">
@@ -4161,22 +3973,22 @@
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A80" s="7"/>
-      <c r="B80" s="8" t="s">
+      <c r="A80" s="5"/>
+      <c r="B80" s="6" t="s">
         <v>30</v>
       </c>
-      <c r="C80" s="8">
+      <c r="C80" s="6">
         <v>9000</v>
       </c>
-      <c r="D80" s="8">
+      <c r="D80" s="6">
         <v>24</v>
       </c>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7" t="b">
+      <c r="E80" s="5"/>
+      <c r="F80" s="5" t="b">
         <f t="shared" si="1"/>
         <v>1</v>
       </c>
-      <c r="G80" s="7"/>
+      <c r="G80" s="5"/>
       <c r="I80" t="str">
         <f t="shared" si="2"/>
         <v>ADULT FROM MAHARASTRA</v>
@@ -4191,27 +4003,27 @@
       </c>
     </row>
     <row r="86" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B86" s="4" t="s">
+      <c r="B86" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C86" s="4" t="s">
+      <c r="C86" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D86" s="4" t="s">
+      <c r="D86" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="F86" s="6" t="s">
+      <c r="F86" s="4" t="s">
         <v>41</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B87" s="5" t="s">
+      <c r="B87" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C87" s="5">
+      <c r="C87" s="3">
         <v>4000</v>
       </c>
-      <c r="D87" s="5">
+      <c r="D87" s="3">
         <v>17</v>
       </c>
       <c r="F87" t="b">
@@ -4220,13 +4032,13 @@
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B88" s="5" t="s">
+      <c r="B88" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C88" s="5">
+      <c r="C88" s="3">
         <v>5600</v>
       </c>
-      <c r="D88" s="5">
+      <c r="D88" s="3">
         <v>18</v>
       </c>
       <c r="F88" t="b">
@@ -4235,13 +4047,13 @@
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B89" s="5" t="s">
+      <c r="B89" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C89" s="5">
+      <c r="C89" s="3">
         <v>9700</v>
       </c>
-      <c r="D89" s="5">
+      <c r="D89" s="3">
         <v>19</v>
       </c>
       <c r="F89" t="b">
@@ -4250,13 +4062,13 @@
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B90" s="5" t="s">
+      <c r="B90" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C90" s="5">
+      <c r="C90" s="3">
         <v>4000</v>
       </c>
-      <c r="D90" s="5">
+      <c r="D90" s="3">
         <v>20</v>
       </c>
       <c r="F90" t="b">
@@ -4265,13 +4077,13 @@
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B91" s="9" t="s">
+      <c r="B91" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C91" s="9">
+      <c r="C91" s="3">
         <v>8000</v>
       </c>
-      <c r="D91" s="9">
+      <c r="D91" s="3">
         <v>21</v>
       </c>
       <c r="F91" t="b">
@@ -4280,31 +4092,31 @@
       </c>
     </row>
     <row r="92" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A92" s="10"/>
-      <c r="B92" s="11" t="s">
+      <c r="A92" s="7"/>
+      <c r="B92" s="8" t="s">
         <v>31</v>
       </c>
-      <c r="C92" s="11">
+      <c r="C92" s="8">
         <v>9000</v>
       </c>
-      <c r="D92" s="11">
+      <c r="D92" s="8">
         <v>17</v>
       </c>
-      <c r="E92" s="10"/>
+      <c r="E92" s="7"/>
       <c r="F92" t="b">
         <f>OR(B92="MH",D92&gt;=18,C92&gt;5000)</f>
         <v>1</v>
       </c>
-      <c r="G92" s="10"/>
+      <c r="G92" s="7"/>
     </row>
     <row r="93" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B93" s="5" t="s">
+      <c r="B93" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C93" s="5">
+      <c r="C93" s="3">
         <v>15000</v>
       </c>
-      <c r="D93" s="5">
+      <c r="D93" s="3">
         <v>18</v>
       </c>
       <c r="F93" t="b">
@@ -4313,13 +4125,13 @@
       </c>
     </row>
     <row r="94" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B94" s="5" t="s">
+      <c r="B94" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C94" s="5">
+      <c r="C94" s="3">
         <v>34000</v>
       </c>
-      <c r="D94" s="5">
+      <c r="D94" s="3">
         <v>16</v>
       </c>
       <c r="F94" t="b">
@@ -4328,13 +4140,13 @@
       </c>
     </row>
     <row r="95" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B95" s="5" t="s">
+      <c r="B95" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C95" s="5">
+      <c r="C95" s="3">
         <v>9000</v>
       </c>
-      <c r="D95" s="5">
+      <c r="D95" s="3">
         <v>20</v>
       </c>
       <c r="F95" t="b">
@@ -4343,13 +4155,13 @@
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B96" s="9" t="s">
+      <c r="B96" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C96" s="9">
+      <c r="C96" s="3">
         <v>9000</v>
       </c>
-      <c r="D96" s="9">
+      <c r="D96" s="3">
         <v>24</v>
       </c>
       <c r="F96" t="b">
@@ -4358,14 +4170,14 @@
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A99" s="12"/>
-      <c r="B99" s="12"/>
-      <c r="C99" s="12"/>
-      <c r="D99" s="12"/>
-      <c r="E99" s="12"/>
-      <c r="F99" s="12"/>
-      <c r="G99" s="12"/>
-      <c r="H99" s="12"/>
+      <c r="A99" s="9"/>
+      <c r="B99" s="9"/>
+      <c r="C99" s="9"/>
+      <c r="D99" s="9"/>
+      <c r="E99" s="9"/>
+      <c r="F99" s="9"/>
+      <c r="G99" s="9"/>
+      <c r="H99" s="9"/>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
       <c r="B101" t="s">
@@ -4411,14 +4223,14 @@
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
-      <c r="A109" s="12"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="12"/>
-      <c r="D109" s="12"/>
-      <c r="E109" s="12"/>
-      <c r="F109" s="12"/>
-      <c r="G109" s="12"/>
-      <c r="H109" s="12"/>
+      <c r="A109" s="9"/>
+      <c r="B109" s="9"/>
+      <c r="C109" s="9"/>
+      <c r="D109" s="9"/>
+      <c r="E109" s="9"/>
+      <c r="F109" s="9"/>
+      <c r="G109" s="9"/>
+      <c r="H109" s="9"/>
     </row>
     <row r="113" spans="2:7" x14ac:dyDescent="0.2">
       <c r="B113" t="s">
@@ -4522,7 +4334,7 @@
       </c>
     </row>
     <row r="124" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B124" s="13" t="str">
+      <c r="B124" s="10" t="str">
         <f>"3"</f>
         <v>3</v>
       </c>
@@ -4546,12 +4358,12 @@
       </c>
     </row>
     <row r="128" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="C128" s="14" t="s">
+      <c r="C128" s="11" t="s">
         <v>60</v>
       </c>
     </row>
     <row r="129" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="C129" s="14" t="str">
+      <c r="C129" s="11" t="str">
         <f>" "</f>
         <v xml:space="preserve"> </v>
       </c>
@@ -4561,13 +4373,13 @@
       </c>
     </row>
     <row r="131" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="A131" s="3"/>
-      <c r="B131" s="3"/>
-      <c r="C131" s="3"/>
-      <c r="D131" s="3"/>
-      <c r="E131" s="3"/>
-      <c r="F131" s="3"/>
-      <c r="G131" s="3"/>
+      <c r="A131" s="1"/>
+      <c r="B131" s="1"/>
+      <c r="C131" s="1"/>
+      <c r="D131" s="1"/>
+      <c r="E131" s="1"/>
+      <c r="F131" s="1"/>
+      <c r="G131" s="1"/>
     </row>
     <row r="134" spans="1:7" x14ac:dyDescent="0.2">
       <c r="B134" t="s">
@@ -4575,24 +4387,24 @@
       </c>
     </row>
     <row r="137" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B137" s="4" t="s">
+      <c r="B137" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="C137" s="4" t="s">
+      <c r="C137" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="D137" s="4" t="s">
+      <c r="D137" s="2" t="s">
         <v>11</v>
       </c>
     </row>
     <row r="138" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B138" s="5" t="s">
+      <c r="B138" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C138" s="5">
+      <c r="C138" s="3">
         <v>4000</v>
       </c>
-      <c r="D138" s="5">
+      <c r="D138" s="3">
         <v>17</v>
       </c>
       <c r="F138" t="str" cm="1">
@@ -4601,13 +4413,13 @@
       </c>
     </row>
     <row r="139" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B139" s="5" t="s">
+      <c r="B139" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C139" s="5">
+      <c r="C139" s="3">
         <v>5600</v>
       </c>
-      <c r="D139" s="5">
+      <c r="D139" s="3">
         <v>18</v>
       </c>
       <c r="F139" t="str" cm="1">
@@ -4616,13 +4428,13 @@
       </c>
     </row>
     <row r="140" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B140" s="5" t="s">
+      <c r="B140" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C140" s="5">
+      <c r="C140" s="3">
         <v>9700</v>
       </c>
-      <c r="D140" s="5">
+      <c r="D140" s="3">
         <v>19</v>
       </c>
       <c r="F140" t="str" cm="1">
@@ -4631,13 +4443,13 @@
       </c>
     </row>
     <row r="141" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B141" s="5" t="s">
+      <c r="B141" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="C141" s="5">
+      <c r="C141" s="3">
         <v>4000</v>
       </c>
-      <c r="D141" s="5">
+      <c r="D141" s="3">
         <v>20</v>
       </c>
       <c r="F141" t="str" cm="1">
@@ -4646,13 +4458,13 @@
       </c>
     </row>
     <row r="142" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B142" s="9" t="s">
+      <c r="B142" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C142" s="9">
+      <c r="C142" s="3">
         <v>8000</v>
       </c>
-      <c r="D142" s="9">
+      <c r="D142" s="3">
         <v>21</v>
       </c>
       <c r="F142" t="str" cm="1">
@@ -4661,13 +4473,13 @@
       </c>
     </row>
     <row r="143" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B143" s="9" t="s">
+      <c r="B143" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="C143" s="9">
+      <c r="C143" s="3">
         <v>9000</v>
       </c>
-      <c r="D143" s="9">
+      <c r="D143" s="3">
         <v>17</v>
       </c>
       <c r="F143" t="e" cm="1">
@@ -4676,13 +4488,13 @@
       </c>
     </row>
     <row r="144" spans="1:7" x14ac:dyDescent="0.2">
-      <c r="B144" s="5" t="s">
+      <c r="B144" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="C144" s="5">
+      <c r="C144" s="3">
         <v>15000</v>
       </c>
-      <c r="D144" s="5">
+      <c r="D144" s="3">
         <v>18</v>
       </c>
       <c r="F144" t="str" cm="1">
@@ -4691,13 +4503,13 @@
       </c>
     </row>
     <row r="145" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B145" s="5" t="s">
+      <c r="B145" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C145" s="5">
+      <c r="C145" s="3">
         <v>34000</v>
       </c>
-      <c r="D145" s="5">
+      <c r="D145" s="3">
         <v>16</v>
       </c>
       <c r="F145" t="str" cm="1">
@@ -4706,13 +4518,13 @@
       </c>
     </row>
     <row r="146" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B146" s="5" t="s">
+      <c r="B146" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="C146" s="5">
+      <c r="C146" s="3">
         <v>9000</v>
       </c>
-      <c r="D146" s="5">
+      <c r="D146" s="3">
         <v>20</v>
       </c>
       <c r="F146" t="str" cm="1">
@@ -4721,13 +4533,13 @@
       </c>
     </row>
     <row r="147" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B147" s="9" t="s">
+      <c r="B147" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="C147" s="9">
+      <c r="C147" s="3">
         <v>9000</v>
       </c>
-      <c r="D147" s="9">
+      <c r="D147" s="3">
         <v>24</v>
       </c>
       <c r="F147" t="str" cm="1">
@@ -4736,7 +4548,7 @@
       </c>
     </row>
     <row r="150" spans="2:7" x14ac:dyDescent="0.2">
-      <c r="B150" s="15" t="s">
+      <c r="B150" s="12" t="s">
         <v>62</v>
       </c>
     </row>
@@ -4909,157 +4721,157 @@
       </c>
     </row>
     <row r="17" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C17" s="16" t="s">
+      <c r="C17" s="13" t="s">
         <v>80</v>
       </c>
     </row>
     <row r="18" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C18" s="16" t="s">
+      <c r="C18" s="13" t="s">
         <v>81</v>
       </c>
     </row>
     <row r="19" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C19" s="16" t="s">
+      <c r="C19" s="13" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="20" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C20" s="16" t="s">
+      <c r="C20" s="13" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="21" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C21" s="16" t="s">
+      <c r="C21" s="13" t="s">
         <v>84</v>
       </c>
     </row>
     <row r="22" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C22" s="16" t="s">
+      <c r="C22" s="13" t="s">
         <v>85</v>
       </c>
     </row>
     <row r="23" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C23" s="16" t="s">
+      <c r="C23" s="13" t="s">
         <v>86</v>
       </c>
     </row>
     <row r="24" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C24" s="16" t="s">
+      <c r="C24" s="13" t="s">
         <v>87</v>
       </c>
     </row>
     <row r="25" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C25" s="16" t="s">
+      <c r="C25" s="13" t="s">
         <v>88</v>
       </c>
     </row>
     <row r="26" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C26" s="16" t="s">
+      <c r="C26" s="13" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="27" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C27" s="16" t="s">
+      <c r="C27" s="13" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="28" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C28" s="16" t="s">
+      <c r="C28" s="13" t="s">
         <v>91</v>
       </c>
     </row>
     <row r="29" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C29" s="16" t="s">
+      <c r="C29" s="13" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="30" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C30" s="16" t="s">
+      <c r="C30" s="13" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="31" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C31" s="16" t="s">
+      <c r="C31" s="13" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="32" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C32" s="16" t="s">
+      <c r="C32" s="13" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="33" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C33" s="16" t="s">
+      <c r="C33" s="13" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="34" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C34" s="16" t="s">
+      <c r="C34" s="13" t="s">
         <v>97</v>
       </c>
     </row>
     <row r="35" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C35" s="16" t="s">
+      <c r="C35" s="13" t="s">
         <v>98</v>
       </c>
     </row>
     <row r="36" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C36" s="16" t="s">
+      <c r="C36" s="13" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="37" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C37" s="16" t="s">
+      <c r="C37" s="13" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="38" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C38" s="16" t="s">
+      <c r="C38" s="13" t="s">
         <v>101</v>
       </c>
     </row>
     <row r="39" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C39" s="16" t="s">
+      <c r="C39" s="13" t="s">
         <v>102</v>
       </c>
     </row>
     <row r="40" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C40" s="16" t="s">
+      <c r="C40" s="13" t="s">
         <v>103</v>
       </c>
     </row>
     <row r="41" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C41" s="16" t="s">
+      <c r="C41" s="13" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="42" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C42" s="16" t="s">
+      <c r="C42" s="13" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="43" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C43" s="16" t="s">
+      <c r="C43" s="13" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="44" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C44" s="16" t="s">
+      <c r="C44" s="13" t="s">
         <v>107</v>
       </c>
     </row>
     <row r="45" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C45" s="16" t="s">
+      <c r="C45" s="13" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="46" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C46" s="16" t="s">
+      <c r="C46" s="13" t="s">
         <v>109</v>
       </c>
     </row>
     <row r="47" spans="3:3" ht="17" x14ac:dyDescent="0.25">
-      <c r="C47" s="16" t="s">
+      <c r="C47" s="13" t="s">
         <v>110</v>
       </c>
     </row>
@@ -5070,7 +4882,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E4CCD3D-4A18-9948-BA45-3DE0C9A01245}">
-  <dimension ref="B1:N71"/>
+  <dimension ref="B1:O71"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="14.83203125" bestFit="1" customWidth="1"/>
@@ -5079,546 +4891,629 @@
     <col min="6" max="6" width="11.1640625" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="12.1640625" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="11.1640625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="21.6640625" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="11" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="40.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B1" s="18" t="s">
+      <c r="B1" s="15" t="s">
         <v>111</v>
       </c>
-      <c r="C1" s="18" t="s">
+      <c r="C1" s="15" t="s">
         <v>29</v>
       </c>
     </row>
     <row r="2" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B2" s="17">
+      <c r="B2" s="14">
         <v>1.1000000000000001</v>
       </c>
-      <c r="C2" s="17">
+      <c r="C2" s="14">
         <v>39343</v>
       </c>
     </row>
     <row r="3" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B3" s="17">
+      <c r="B3" s="14">
         <v>1.3</v>
       </c>
-      <c r="C3" s="17">
+      <c r="C3" s="14">
         <v>46205</v>
       </c>
     </row>
     <row r="4" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B4" s="17">
+      <c r="B4" s="14">
         <v>1.5</v>
       </c>
-      <c r="C4" s="17">
+      <c r="C4" s="14">
         <v>37731</v>
       </c>
     </row>
     <row r="5" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B5" s="17">
+      <c r="B5" s="14">
         <v>2</v>
       </c>
-      <c r="C5" s="17">
+      <c r="C5" s="14">
         <v>43525</v>
       </c>
     </row>
     <row r="6" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B6" s="17">
+      <c r="B6" s="14">
         <v>2.2000000000000002</v>
       </c>
-      <c r="C6" s="17">
+      <c r="C6" s="14">
         <v>39891</v>
       </c>
-      <c r="K6" s="2" t="s">
+      <c r="K6" s="19" t="s">
         <v>112</v>
       </c>
-      <c r="L6" s="2"/>
+      <c r="L6" s="19"/>
       <c r="N6" t="s">
         <v>113</v>
       </c>
     </row>
     <row r="7" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B7" s="17">
+      <c r="B7" s="14">
         <v>2.9</v>
       </c>
-      <c r="C7" s="17">
+      <c r="C7" s="14">
         <v>56642</v>
       </c>
-      <c r="K7" s="2"/>
-      <c r="L7" s="2"/>
+      <c r="K7" s="19"/>
+      <c r="L7" s="19"/>
     </row>
     <row r="8" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B8" s="17">
+      <c r="B8" s="14">
         <v>3</v>
       </c>
-      <c r="C8" s="17">
+      <c r="C8" s="14">
         <v>60150</v>
       </c>
     </row>
     <row r="9" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B9" s="17">
+      <c r="B9" s="14">
         <v>3.2</v>
       </c>
-      <c r="C9" s="17">
+      <c r="C9" s="14">
         <v>54445</v>
       </c>
     </row>
     <row r="10" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B10" s="17">
+      <c r="B10" s="14">
         <v>3.2</v>
       </c>
-      <c r="C10" s="17">
+      <c r="C10" s="14">
         <v>64445</v>
       </c>
     </row>
     <row r="11" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B11" s="17">
+      <c r="B11" s="14">
         <v>3.7</v>
       </c>
-      <c r="C11" s="17">
+      <c r="C11" s="14">
         <v>57189</v>
       </c>
     </row>
     <row r="12" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B12" s="17">
+      <c r="B12" s="14">
         <v>3.9</v>
       </c>
-      <c r="C12" s="17">
+      <c r="C12" s="14">
         <v>63218</v>
       </c>
     </row>
     <row r="13" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B13" s="17">
+      <c r="B13" s="14">
         <v>4</v>
       </c>
-      <c r="C13" s="17">
+      <c r="C13" s="14">
         <v>55794</v>
       </c>
     </row>
     <row r="14" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B14" s="17">
+      <c r="B14" s="14">
         <v>4</v>
       </c>
-      <c r="C14" s="17">
+      <c r="C14" s="14">
         <v>56957</v>
       </c>
     </row>
     <row r="15" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B15" s="17">
+      <c r="B15" s="14">
         <v>4.0999999999999996</v>
       </c>
-      <c r="C15" s="17">
+      <c r="C15" s="14">
         <v>57081</v>
       </c>
     </row>
     <row r="16" spans="2:14" x14ac:dyDescent="0.2">
-      <c r="B16" s="17">
+      <c r="B16" s="14">
         <v>4.5</v>
       </c>
-      <c r="C16" s="17">
+      <c r="C16" s="14">
         <v>61111</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B17" s="17">
+    <row r="17" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B17" s="14">
         <v>4.9000000000000004</v>
       </c>
-      <c r="C17" s="17">
+      <c r="C17" s="14">
         <v>67938</v>
       </c>
     </row>
-    <row r="18" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B18" s="17">
+    <row r="18" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B18" s="14">
         <v>5.0999999999999996</v>
       </c>
-      <c r="C18" s="17">
+      <c r="C18" s="14">
         <v>66029</v>
       </c>
     </row>
-    <row r="19" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B19" s="17">
+    <row r="19" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B19" s="14">
         <v>5.3</v>
       </c>
-      <c r="C19" s="17">
+      <c r="C19" s="14">
         <v>83088</v>
       </c>
       <c r="E19" t="s">
         <v>114</v>
       </c>
-      <c r="K19" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="20" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B20" s="17">
+      <c r="L19" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="20" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B20" s="14">
         <v>5.9</v>
       </c>
-      <c r="C20" s="17">
+      <c r="C20" s="14">
         <v>81363</v>
       </c>
-      <c r="K20" t="s">
-        <v>139</v>
-      </c>
-    </row>
-    <row r="21" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B21" s="17">
+    </row>
+    <row r="21" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B21" s="14">
         <v>6</v>
       </c>
-      <c r="C21" s="17">
+      <c r="C21" s="14">
         <v>93940</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="24" t="s">
         <v>115</v>
       </c>
-      <c r="F21" s="22"/>
-      <c r="K21" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="22" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B22" s="17">
+      <c r="F21" s="24"/>
+    </row>
+    <row r="22" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B22" s="14">
         <v>6.8</v>
       </c>
-      <c r="C22" s="17">
+      <c r="C22" s="14">
         <v>91738</v>
       </c>
-      <c r="E22" s="19" t="s">
+      <c r="E22" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="F22" s="19">
+      <c r="F22" s="21">
         <v>0.9782416184887599</v>
       </c>
     </row>
-    <row r="23" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B23" s="17">
+    <row r="23" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B23" s="14">
         <v>7.1</v>
       </c>
-      <c r="C23" s="17">
+      <c r="C23" s="14">
         <v>98273</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E23" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="F23" s="28">
+      <c r="F23" s="21">
         <v>0.95695666414350844</v>
       </c>
     </row>
-    <row r="24" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B24" s="17">
+    <row r="24" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B24" s="14">
         <v>7.9</v>
       </c>
-      <c r="C24" s="17">
+      <c r="C24" s="14">
         <v>101302</v>
       </c>
-      <c r="E24" s="28" t="s">
+      <c r="E24" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="F24" s="28">
+      <c r="F24" s="21">
         <v>0.95541940214863375</v>
       </c>
     </row>
-    <row r="25" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B25" s="17">
+    <row r="25" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B25" s="14">
         <v>8.1999999999999993</v>
       </c>
-      <c r="C25" s="17">
+      <c r="C25" s="14">
         <v>113812</v>
       </c>
-      <c r="E25" s="19" t="s">
+      <c r="E25" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="F25" s="19">
+      <c r="F25" s="21">
         <v>5788.3150511193935</v>
       </c>
     </row>
-    <row r="26" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B26" s="17">
+    <row r="26" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B26" s="14">
         <v>8.6999999999999993</v>
       </c>
-      <c r="C26" s="17">
+      <c r="C26" s="14">
         <v>109431</v>
       </c>
-      <c r="E26" s="20" t="s">
+      <c r="E26" s="22" t="s">
         <v>120</v>
       </c>
-      <c r="F26" s="20">
+      <c r="F26" s="22">
         <v>30</v>
       </c>
     </row>
-    <row r="27" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B27" s="17">
+    <row r="27" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B27" s="14">
         <v>9</v>
       </c>
-      <c r="C27" s="17">
+      <c r="C27" s="14">
         <v>105582</v>
       </c>
     </row>
-    <row r="28" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="B28" s="17">
+    <row r="28" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="B28" s="14">
         <v>9.5</v>
       </c>
-      <c r="C28" s="17">
+      <c r="C28" s="14">
         <v>116969</v>
       </c>
       <c r="E28" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="29" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B29" s="17">
+    <row r="29" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B29" s="14">
         <v>9.6</v>
       </c>
-      <c r="C29" s="17">
+      <c r="C29" s="14">
         <v>112635</v>
       </c>
-      <c r="E29" s="21"/>
-      <c r="F29" s="21" t="s">
+      <c r="E29" s="23"/>
+      <c r="F29" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="G29" s="21" t="s">
+      <c r="G29" s="23" t="s">
         <v>127</v>
       </c>
-      <c r="H29" s="21" t="s">
+      <c r="H29" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="I29" s="21" t="s">
+      <c r="I29" s="23" t="s">
         <v>129</v>
       </c>
-      <c r="J29" s="21" t="s">
+      <c r="J29" s="23" t="s">
         <v>130</v>
       </c>
     </row>
-    <row r="30" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B30" s="17">
+    <row r="30" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B30" s="14">
         <v>10.3</v>
       </c>
-      <c r="C30" s="17">
+      <c r="C30" s="14">
         <v>122391</v>
       </c>
-      <c r="E30" s="19" t="s">
+      <c r="E30" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="F30" s="19">
+      <c r="F30" s="21">
         <v>1</v>
       </c>
-      <c r="G30" s="19">
+      <c r="G30" s="21">
         <v>20856849300.33157</v>
       </c>
-      <c r="H30" s="19">
+      <c r="H30" s="21">
         <v>20856849300.33157</v>
       </c>
-      <c r="I30" s="19">
+      <c r="I30" s="21">
         <v>622.50720263302401</v>
       </c>
-      <c r="J30" s="19">
+      <c r="J30" s="21">
         <v>1.1430681092271349E-20</v>
       </c>
     </row>
-    <row r="31" spans="2:11" x14ac:dyDescent="0.2">
-      <c r="B31" s="17">
+    <row r="31" spans="2:12" x14ac:dyDescent="0.2">
+      <c r="B31" s="14">
         <v>10.5</v>
       </c>
-      <c r="C31" s="17">
+      <c r="C31" s="14">
         <v>121872</v>
       </c>
-      <c r="E31" s="19" t="s">
+      <c r="E31" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="F31" s="19">
+      <c r="F31" s="21">
         <v>28</v>
       </c>
-      <c r="G31" s="19">
+      <c r="G31" s="21">
         <v>938128551.66842878</v>
       </c>
-      <c r="H31" s="19">
+      <c r="H31" s="21">
         <v>33504591.131015312</v>
       </c>
-      <c r="I31" s="19"/>
-      <c r="J31" s="19"/>
-    </row>
-    <row r="32" spans="2:11" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E32" s="20" t="s">
+      <c r="I31" s="21"/>
+      <c r="J31" s="21"/>
+    </row>
+    <row r="32" spans="2:12" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E32" s="22" t="s">
         <v>124</v>
       </c>
-      <c r="F32" s="20">
+      <c r="F32" s="22">
         <v>29</v>
       </c>
-      <c r="G32" s="20">
+      <c r="G32" s="22">
         <v>21794977852</v>
       </c>
-      <c r="H32" s="20"/>
-      <c r="I32" s="20"/>
-      <c r="J32" s="20"/>
-    </row>
-    <row r="33" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
-    <row r="34" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E34" s="21"/>
-      <c r="F34" s="25" t="s">
+      <c r="H32" s="22"/>
+      <c r="I32" s="22"/>
+      <c r="J32" s="22"/>
+    </row>
+    <row r="33" spans="5:15" ht="17" thickBot="1" x14ac:dyDescent="0.25"/>
+    <row r="34" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="E34" s="23"/>
+      <c r="F34" s="23" t="s">
         <v>131</v>
       </c>
-      <c r="G34" s="21" t="s">
+      <c r="G34" s="23" t="s">
         <v>119</v>
       </c>
-      <c r="H34" s="21" t="s">
+      <c r="H34" s="23" t="s">
         <v>132</v>
       </c>
-      <c r="I34" s="21" t="s">
+      <c r="I34" s="23" t="s">
         <v>133</v>
       </c>
-      <c r="J34" s="21" t="s">
+      <c r="J34" s="23" t="s">
         <v>134</v>
       </c>
-      <c r="K34" s="21" t="s">
+      <c r="K34" s="23" t="s">
         <v>135</v>
       </c>
-      <c r="L34" s="21" t="s">
+      <c r="L34" s="23" t="s">
+        <v>149</v>
+      </c>
+      <c r="M34" s="23" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="35" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="E35" s="21" t="s">
+        <v>125</v>
+      </c>
+      <c r="F35" s="21">
+        <v>25792.200198668696</v>
+      </c>
+      <c r="G35" s="21">
+        <v>2273.0534325816047</v>
+      </c>
+      <c r="H35" s="21">
+        <v>11.346939684288628</v>
+      </c>
+      <c r="I35" s="21">
+        <v>5.5119502709561397E-12</v>
+      </c>
+      <c r="J35" s="21">
+        <v>21136.061313686339</v>
+      </c>
+      <c r="K35" s="21">
+        <v>30448.339083651052</v>
+      </c>
+      <c r="L35" s="21">
+        <v>19511.156989158186</v>
+      </c>
+      <c r="M35" s="21">
+        <v>32073.243408179205</v>
+      </c>
+    </row>
+    <row r="36" spans="5:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E36" s="22" t="s">
+        <v>111</v>
+      </c>
+      <c r="F36" s="22">
+        <v>9449.9623214550757</v>
+      </c>
+      <c r="G36" s="22">
+        <v>378.75457423882102</v>
+      </c>
+      <c r="H36" s="22">
+        <v>24.950094240964781</v>
+      </c>
+      <c r="I36" s="22">
+        <v>1.1430681092271349E-20</v>
+      </c>
+      <c r="J36" s="22">
+        <v>8674.1187465966577</v>
+      </c>
+      <c r="K36" s="22">
+        <v>10225.805896313494</v>
+      </c>
+      <c r="L36" s="22">
+        <v>8403.3640266266575</v>
+      </c>
+      <c r="M36" s="22">
+        <v>10496.560616283494</v>
+      </c>
+    </row>
+    <row r="40" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="I40" t="s">
+        <v>142</v>
+      </c>
+    </row>
+    <row r="41" spans="5:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="E41" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="L42" s="23"/>
+      <c r="M42" s="23"/>
+      <c r="N42" s="23"/>
+      <c r="O42" s="23"/>
+    </row>
+    <row r="43" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="F43" s="12" t="s">
         <v>136</v>
       </c>
-      <c r="M34" s="21" t="s">
+      <c r="G43" s="12"/>
+      <c r="H43" s="12"/>
+      <c r="L43" s="21"/>
+      <c r="M43" s="21"/>
+      <c r="N43" s="21"/>
+      <c r="O43" s="21"/>
+    </row>
+    <row r="44" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
+      <c r="N44" s="21"/>
+      <c r="O44" s="21"/>
+    </row>
+    <row r="45" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="L45" s="21"/>
+      <c r="M45" s="21"/>
+      <c r="N45" s="21"/>
+      <c r="O45" s="21"/>
+    </row>
+    <row r="46" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="F46" t="s">
+        <v>140</v>
+      </c>
+      <c r="L46" s="21"/>
+      <c r="M46" s="21"/>
+      <c r="N46" s="21"/>
+      <c r="O46" s="21"/>
+    </row>
+    <row r="47" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="L47" s="21"/>
+      <c r="M47" s="21"/>
+      <c r="N47" s="21"/>
+      <c r="O47" s="21"/>
+    </row>
+    <row r="48" spans="5:15" x14ac:dyDescent="0.2">
+      <c r="F48" t="s">
+        <v>143</v>
+      </c>
+      <c r="L48" s="21"/>
+      <c r="M48" s="21"/>
+      <c r="N48" s="21"/>
+      <c r="O48" s="21"/>
+    </row>
+    <row r="49" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="F49" t="s">
+        <v>141</v>
+      </c>
+      <c r="I49" t="s">
+        <v>145</v>
+      </c>
+      <c r="L49" s="21"/>
+      <c r="M49" s="21"/>
+      <c r="N49" s="21"/>
+      <c r="O49" s="21"/>
+    </row>
+    <row r="50" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="L50" s="21"/>
+      <c r="M50" s="21"/>
+      <c r="N50" s="21"/>
+      <c r="O50" s="21"/>
+    </row>
+    <row r="51" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="E51" t="s">
+        <v>144</v>
+      </c>
+      <c r="L51" s="21"/>
+      <c r="M51" s="21"/>
+      <c r="N51" s="21"/>
+      <c r="O51" s="21"/>
+    </row>
+    <row r="52" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="E52" t="s">
+        <v>146</v>
+      </c>
+      <c r="L52" s="21"/>
+      <c r="M52" s="21"/>
+      <c r="N52" s="21"/>
+      <c r="O52" s="21"/>
+    </row>
+    <row r="53" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="L53" s="21"/>
+      <c r="M53" s="21"/>
+      <c r="N53" s="21"/>
+      <c r="O53" s="21"/>
+    </row>
+    <row r="54" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="L54" s="21"/>
+      <c r="M54" s="21"/>
+      <c r="N54" s="21"/>
+      <c r="O54" s="21"/>
+    </row>
+    <row r="55" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="L55" s="21"/>
+      <c r="M55" s="21"/>
+      <c r="N55" s="21"/>
+      <c r="O55" s="21"/>
+    </row>
+    <row r="56" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="L56" s="21"/>
+      <c r="M56" s="21"/>
+      <c r="N56" s="21"/>
+      <c r="O56" s="21"/>
+    </row>
+    <row r="57" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="D57" s="17" t="s">
         <v>137</v>
       </c>
-    </row>
-    <row r="35" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E35" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="F35" s="26">
-        <v>25792.200198668696</v>
-      </c>
-      <c r="G35" s="19">
-        <v>2273.0534325816047</v>
-      </c>
-      <c r="H35" s="19">
-        <v>11.346939684288628</v>
-      </c>
-      <c r="I35" s="19">
-        <v>5.5119502709561397E-12</v>
-      </c>
-      <c r="J35" s="19">
-        <v>21136.061313686339</v>
-      </c>
-      <c r="K35" s="19">
-        <v>30448.339083651052</v>
-      </c>
-      <c r="L35" s="19">
-        <v>21136.061313686339</v>
-      </c>
-      <c r="M35" s="19">
-        <v>30448.339083651052</v>
-      </c>
-    </row>
-    <row r="36" spans="5:13" ht="17" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="E36" s="20" t="s">
-        <v>111</v>
-      </c>
-      <c r="F36" s="27">
-        <v>9449.9623214550757</v>
-      </c>
-      <c r="G36" s="20">
-        <v>378.75457423882102</v>
-      </c>
-      <c r="H36" s="20">
-        <v>24.950094240964781</v>
-      </c>
-      <c r="I36" s="20">
-        <v>1.1430681092271349E-20</v>
-      </c>
-      <c r="J36" s="20">
-        <v>8674.1187465966577</v>
-      </c>
-      <c r="K36" s="20">
-        <v>10225.805896313494</v>
-      </c>
-      <c r="L36" s="20">
-        <v>8674.1187465966577</v>
-      </c>
-      <c r="M36" s="20">
-        <v>10225.805896313494</v>
-      </c>
-    </row>
-    <row r="39" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E39" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="40" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="I40" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="41" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="E41" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="43" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="F43" s="23" t="s">
-        <v>138</v>
-      </c>
-      <c r="G43" s="23"/>
-      <c r="H43" s="23"/>
-    </row>
-    <row r="46" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="F46" t="s">
-        <v>143</v>
-      </c>
-    </row>
-    <row r="48" spans="5:13" x14ac:dyDescent="0.2">
-      <c r="F48" t="s">
-        <v>146</v>
-      </c>
-    </row>
-    <row r="49" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="F49" t="s">
-        <v>144</v>
-      </c>
-      <c r="I49" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="51" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="E51" t="s">
-        <v>147</v>
-      </c>
-    </row>
-    <row r="52" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="E52" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="54" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="D54" s="24"/>
-      <c r="E54" s="24"/>
-      <c r="F54" s="24"/>
-      <c r="G54" s="24"/>
-      <c r="H54" s="24"/>
-      <c r="I54" s="24"/>
-    </row>
-    <row r="57" spans="4:9" x14ac:dyDescent="0.2">
-      <c r="D57" s="30" t="s">
-        <v>139</v>
-      </c>
-      <c r="E57" s="30"/>
-      <c r="F57" s="30"/>
-    </row>
-    <row r="61" spans="4:9" x14ac:dyDescent="0.2">
+      <c r="E57" s="17"/>
+      <c r="F57" s="17"/>
+      <c r="L57" s="21"/>
+      <c r="M57" s="21"/>
+      <c r="N57" s="21"/>
+      <c r="O57" s="21"/>
+    </row>
+    <row r="58" spans="4:15" x14ac:dyDescent="0.2">
+      <c r="L58" s="21"/>
+      <c r="M58" s="21"/>
+      <c r="N58" s="21"/>
+      <c r="O58" s="21"/>
+    </row>
+    <row r="59" spans="4:15" ht="17" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="L59" s="22"/>
+      <c r="M59" s="22"/>
+      <c r="N59" s="22"/>
+      <c r="O59" s="22"/>
+    </row>
+    <row r="61" spans="4:15" x14ac:dyDescent="0.2">
       <c r="E61" t="str">
         <f>"SALARY = "&amp;ROUND(F35,2)&amp;" + "&amp;ROUND(F36,2)&amp;" * YOE"</f>
         <v>SALARY = 25792.2 + 9449.96 * YOE</v>
       </c>
     </row>
     <row r="65" spans="4:7" x14ac:dyDescent="0.2">
-      <c r="D65" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E65" s="29"/>
-      <c r="F65" s="29"/>
-      <c r="G65" s="29"/>
+      <c r="D65" s="18" t="s">
+        <v>138</v>
+      </c>
+      <c r="E65" s="18"/>
+      <c r="F65" s="18"/>
+      <c r="G65" s="18"/>
     </row>
     <row r="67" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D67" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="E67">
         <f>F23*100</f>
@@ -5627,7 +5522,7 @@
     </row>
     <row r="71" spans="4:7" x14ac:dyDescent="0.2">
       <c r="D71" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
   </sheetData>
